--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128626688</v>
+        <v>128626652</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396022</v>
+        <v>396094</v>
       </c>
       <c r="R2" t="n">
-        <v>7064244</v>
+        <v>7064438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128626682</v>
+        <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>97654</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395992</v>
+        <v>396022</v>
       </c>
       <c r="R3" t="n">
         <v>7064244</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128626652</v>
+        <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>97654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396094</v>
+        <v>395992</v>
       </c>
       <c r="R4" t="n">
-        <v>7064438</v>
+        <v>7064244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626652</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97654</v>
+        <v>97660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128626649</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128626656</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128626680</v>
       </c>
       <c r="B12" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128626651</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128626657</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>128626660</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128626664</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>128626653</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128626646</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128626647</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128626655</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128626661</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>128626663</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128626662</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>128626650</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>128626659</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97654</v>
+        <v>97660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128626645</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>128626654</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97660</v>
+        <v>97666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97660</v>
+        <v>97666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97666</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97666</v>
+        <v>97668</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626652</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97669</v>
+        <v>97696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128626649</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128626656</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128626680</v>
       </c>
       <c r="B12" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128626651</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128626657</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>128626660</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128626664</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>128626653</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128626646</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128626647</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128626655</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128626661</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>128626663</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128626662</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>128626650</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>128626659</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97669</v>
+        <v>97696</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128626645</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>128626654</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97696</v>
+        <v>97702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97696</v>
+        <v>97702</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97702</v>
+        <v>97709</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626652</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128626649</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128626656</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128626680</v>
       </c>
       <c r="B12" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128626651</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128626657</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>128626660</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128626664</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>128626653</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128626646</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128626647</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128626655</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128626661</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>128626663</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128626662</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>128626650</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>128626659</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128626645</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>128626654</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128626652</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128626649</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128626656</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128626680</v>
       </c>
       <c r="B12" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128626651</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128626657</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>128626660</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128626664</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>128626653</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128626646</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>128626647</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128626655</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>128626661</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>128626663</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>128626662</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>128626650</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>128626659</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128626645</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>128626654</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97723</v>
+        <v>97728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91529</v>
+        <v>91534</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97723</v>
+        <v>97728</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128626688</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128626682</v>
       </c>
       <c r="B4" t="n">
-        <v>97728</v>
+        <v>97736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128626676</v>
       </c>
       <c r="B6" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128626639</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128626670</v>
       </c>
       <c r="B9" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128626687</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128626642</v>
       </c>
       <c r="B11" t="n">
-        <v>92218</v>
+        <v>92226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128626675</v>
       </c>
       <c r="B13" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128626673</v>
       </c>
       <c r="B15" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>128626669</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>128626689</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>128626677</v>
       </c>
       <c r="B25" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128626671</v>
       </c>
       <c r="B29" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>128626683</v>
       </c>
       <c r="B30" t="n">
-        <v>91534</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>128626685</v>
       </c>
       <c r="B31" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>128626686</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>128626681</v>
       </c>
       <c r="B35" t="n">
-        <v>97728</v>
+        <v>97736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128626674</v>
       </c>
       <c r="B37" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>128626672</v>
       </c>
       <c r="B39" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128626652</v>
+        <v>128626639</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396094</v>
+        <v>396101</v>
       </c>
       <c r="R2" t="n">
-        <v>7064438</v>
+        <v>7064405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128626688</v>
+        <v>128626683</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396022</v>
+        <v>396120</v>
       </c>
       <c r="R3" t="n">
-        <v>7064244</v>
+        <v>7064282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128626682</v>
+        <v>128626670</v>
       </c>
       <c r="B4" t="n">
-        <v>97736</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395992</v>
+        <v>396129</v>
       </c>
       <c r="R4" t="n">
-        <v>7064244</v>
+        <v>7064280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128626649</v>
+        <v>128626671</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396136</v>
+        <v>396148</v>
       </c>
       <c r="R5" t="n">
-        <v>7064515</v>
+        <v>7064302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128626676</v>
+        <v>128626672</v>
       </c>
       <c r="B6" t="n">
-        <v>79194</v>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396051</v>
+        <v>396165</v>
       </c>
       <c r="R6" t="n">
-        <v>7064385</v>
+        <v>7064332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128626656</v>
+        <v>128626673</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396030</v>
+        <v>396201</v>
       </c>
       <c r="R7" t="n">
-        <v>7064349</v>
+        <v>7064373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128626639</v>
+        <v>128626674</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396101</v>
+        <v>396142</v>
       </c>
       <c r="R8" t="n">
-        <v>7064405</v>
+        <v>7064445</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128626670</v>
+        <v>128626675</v>
       </c>
       <c r="B9" t="n">
-        <v>79194</v>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396129</v>
+        <v>396075</v>
       </c>
       <c r="R9" t="n">
-        <v>7064280</v>
+        <v>7064380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128626687</v>
+        <v>128626676</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395993</v>
+        <v>396051</v>
       </c>
       <c r="R10" t="n">
-        <v>7064355</v>
+        <v>7064385</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128626642</v>
+        <v>128626677</v>
       </c>
       <c r="B11" t="n">
-        <v>92226</v>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>396123</v>
+        <v>395975</v>
       </c>
       <c r="R11" t="n">
-        <v>7064287</v>
+        <v>7064356</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,57 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128626680</v>
+        <v>128626669</v>
       </c>
       <c r="B12" t="n">
-        <v>57827</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gråsjöån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>396044</v>
+        <v>396213</v>
       </c>
       <c r="R12" t="n">
-        <v>7064234</v>
+        <v>7064348</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128626675</v>
+        <v>128626642</v>
       </c>
       <c r="B13" t="n">
-        <v>79194</v>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>396075</v>
+        <v>396123</v>
       </c>
       <c r="R13" t="n">
-        <v>7064380</v>
+        <v>7064287</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128626651</v>
+        <v>128626689</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396108</v>
+        <v>396000</v>
       </c>
       <c r="R14" t="n">
-        <v>7064460</v>
+        <v>7064240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1914,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1968,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128626673</v>
+        <v>128626645</v>
       </c>
       <c r="B15" t="n">
-        <v>79194</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396201</v>
+        <v>396061</v>
       </c>
       <c r="R15" t="n">
-        <v>7064373</v>
+        <v>7064223</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2065,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128626657</v>
+        <v>128626646</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396028</v>
+        <v>396116</v>
       </c>
       <c r="R16" t="n">
-        <v>7064388</v>
+        <v>7064270</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2167,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128626660</v>
+        <v>128626647</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2202,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395994</v>
+        <v>396132</v>
       </c>
       <c r="R17" t="n">
-        <v>7064354</v>
+        <v>7064488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,7 +2220,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128626664</v>
+        <v>128626648</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396011</v>
+        <v>396162</v>
       </c>
       <c r="R18" t="n">
-        <v>7064241</v>
+        <v>7064525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128626653</v>
+        <v>128626649</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2406,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396114</v>
+        <v>396136</v>
       </c>
       <c r="R19" t="n">
-        <v>7064404</v>
+        <v>7064515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,7 +2424,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2473,10 +2451,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128626646</v>
+        <v>128626650</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2508,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396116</v>
+        <v>396125</v>
       </c>
       <c r="R20" t="n">
-        <v>7064270</v>
+        <v>7064497</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2548,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2575,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128626647</v>
+        <v>128626651</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2610,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>396132</v>
+        <v>396108</v>
       </c>
       <c r="R21" t="n">
-        <v>7064488</v>
+        <v>7064460</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,10 +2655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128626655</v>
+        <v>128626652</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396015</v>
+        <v>396094</v>
       </c>
       <c r="R22" t="n">
-        <v>7064343</v>
+        <v>7064438</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2752,7 +2730,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2779,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128626669</v>
+        <v>128626653</v>
       </c>
       <c r="B23" t="n">
-        <v>80141</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2790,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2814,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396213</v>
+        <v>396114</v>
       </c>
       <c r="R23" t="n">
-        <v>7064348</v>
+        <v>7064404</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,6 +2828,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2876,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128626689</v>
+        <v>128626654</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2887,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2911,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>396000</v>
+        <v>396068</v>
       </c>
       <c r="R24" t="n">
-        <v>7064240</v>
+        <v>7064391</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,7 +2934,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,32 +2961,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128626677</v>
+        <v>128626655</v>
       </c>
       <c r="B25" t="n">
-        <v>79194</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3013,10 +2996,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395975</v>
+        <v>396015</v>
       </c>
       <c r="R25" t="n">
-        <v>7064356</v>
+        <v>7064343</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3049,6 +3032,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3075,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128626661</v>
+        <v>128626656</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3110,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395986</v>
+        <v>396030</v>
       </c>
       <c r="R26" t="n">
-        <v>7064362</v>
+        <v>7064349</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,7 +3138,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3177,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128626663</v>
+        <v>128626657</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>395991</v>
+        <v>396028</v>
       </c>
       <c r="R27" t="n">
-        <v>7064246</v>
+        <v>7064388</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,7 +3240,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3279,10 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128626662</v>
+        <v>128626658</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3314,10 +3302,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395978</v>
+        <v>395990</v>
       </c>
       <c r="R28" t="n">
-        <v>7064358</v>
+        <v>7064385</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,32 +3369,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128626671</v>
+        <v>128626659</v>
       </c>
       <c r="B29" t="n">
-        <v>79194</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3416,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>396148</v>
+        <v>395960</v>
       </c>
       <c r="R29" t="n">
-        <v>7064302</v>
+        <v>7064363</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,6 +3440,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3478,10 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128626683</v>
+        <v>128626660</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3489,21 +3482,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3513,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396120</v>
+        <v>395994</v>
       </c>
       <c r="R30" t="n">
-        <v>7064282</v>
+        <v>7064354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3549,6 +3542,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3575,10 +3573,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128626685</v>
+        <v>128626661</v>
       </c>
       <c r="B31" t="n">
-        <v>91544</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3586,21 +3584,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3610,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396138</v>
+        <v>395986</v>
       </c>
       <c r="R31" t="n">
-        <v>7064523</v>
+        <v>7064362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3646,6 +3644,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3672,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128626650</v>
+        <v>128626662</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3707,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396125</v>
+        <v>395978</v>
       </c>
       <c r="R32" t="n">
-        <v>7064497</v>
+        <v>7064358</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,7 +3750,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3774,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128626659</v>
+        <v>128626663</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>395960</v>
+        <v>395991</v>
       </c>
       <c r="R33" t="n">
-        <v>7064363</v>
+        <v>7064246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3849,7 +3852,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3876,10 +3879,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128626686</v>
+        <v>128626664</v>
       </c>
       <c r="B34" t="n">
-        <v>91544</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,21 +3890,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3911,10 +3914,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396085</v>
+        <v>396011</v>
       </c>
       <c r="R34" t="n">
-        <v>7064398</v>
+        <v>7064241</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3947,6 +3950,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3973,45 +3981,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128626681</v>
+        <v>128626680</v>
       </c>
       <c r="B35" t="n">
-        <v>97736</v>
+        <v>58057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220686</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gråsjöån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>395959</v>
+        <v>396044</v>
       </c>
       <c r="R35" t="n">
-        <v>7064354</v>
+        <v>7064234</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,32 +4090,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128626645</v>
+        <v>128626681</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>98194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220686</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4105,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>396061</v>
+        <v>395959</v>
       </c>
       <c r="R36" t="n">
-        <v>7064223</v>
+        <v>7064354</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4141,11 +4161,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4172,32 +4187,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128626674</v>
+        <v>128626682</v>
       </c>
       <c r="B37" t="n">
-        <v>79194</v>
+        <v>98194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>220686</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4207,10 +4222,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>396142</v>
+        <v>395992</v>
       </c>
       <c r="R37" t="n">
-        <v>7064445</v>
+        <v>7064244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4266,205 +4281,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>128626654</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57723</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Gråsjöån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>396068</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7064391</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>128626672</v>
-      </c>
-      <c r="B39" t="n">
-        <v>79194</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Platismatia norvegica</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Gråsjöån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>396165</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7064332</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42592-2024 artfynd.xlsx
+++ b/artfynd/A 42592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626683</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626670</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626672</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626673</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626674</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626675</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626676</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626677</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626669</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626642</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626689</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626645</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626646</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626647</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626648</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626649</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626650</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,6 +2752,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626651</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2754,6 +2859,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626652</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626653</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2958,6 +3073,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626654</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3060,6 +3180,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626655</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3162,6 +3287,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626656</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3264,6 +3394,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626657</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3366,6 +3501,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626658</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3468,6 +3608,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626659</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3570,6 +3715,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626660</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3672,6 +3822,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626661</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3774,6 +3929,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626662</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3876,6 +4036,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626663</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3978,6 +4143,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626664</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4087,6 +4257,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626680</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4184,6 +4359,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626681</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4281,8 +4461,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626682</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>